--- a/PsychoPy/prepost.xlsx
+++ b/PsychoPy/prepost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iowa-my.sharepoint.com/personal/markberardi_uiowa_edu/Documents/Desktop/VDR_Noise/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iowa-my.sharepoint.com/personal/markberardi_uiowa_edu/Documents/Documents/GitHub/VLT-VBAL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83A326D8-FB5E-4BAD-AA17-80D3F518269B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="8_{83A326D8-FB5E-4BAD-AA17-80D3F518269B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A94A664F-F7A7-4614-A5CD-C842F11A4CE6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22770" yWindow="4515" windowWidth="15975" windowHeight="16005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>SpeechText</t>
   </si>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t>isIntro</t>
-  </si>
-  <si>
-    <t>isRFF</t>
   </si>
   <si>
     <t>RFF_rep</t>
@@ -43,90 +40,39 @@
     <t>RatingTF</t>
   </si>
   <si>
-    <t>Bitte lesen Sie nun diesen Text vor.</t>
-  </si>
-  <si>
-    <t>Einst stritten sich Nordwind und Sonne, wer von ihnen beiden wohl der Stärkere wäre, als ein Wanderer, der in einen warmen Mantel gehüllt war, des Weges kam. Sie wurden einig, dass derjenige für den Stärkeren gelten sollte, der den Wanderer zwingen würde, seinen Mantel abzunehmen. Der Nordwind blies mit aller Macht, aber je mehr er blies, desto fester hüllte sich der Wanderer in seinen Mantel ein. Endlich gab der Nordwind den Kampf auf. Nun erwärmte die Sonne die Luft mit ihren freundlichen Strahlen und schon nach wenigen Augenblicken zog der Wanderer seinen Mantel aus. Da musste der Nordwind zugeben, dass die Sonne von ihnen beiden der Stärkere war.</t>
-  </si>
-  <si>
-    <t>LESEN_TEXT.wav</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
-    <t>nordwind</t>
+    <t>SpeechIntroText</t>
   </si>
   <si>
-    <t>Hier ist der erste Satz:
-„In der Auffahrt wächst nie viel Efeu.“
-Bitte lesen Sie die folgenden Sätze.</t>
+    <t>Task</t>
   </si>
   <si>
-    <t xml:space="preserve">In der Auffahrt wächst nie viel Efeu. </t>
+    <t>Reading</t>
   </si>
   <si>
-    <t>LESEN_SAETZE_FF.wav</t>
+    <t>rainbow</t>
   </si>
   <si>
-    <t>RFF_FF</t>
+    <t>READ.wav</t>
   </si>
   <si>
-    <t>Bitte lesen Sie die folgenden Sätze vor.</t>
+    <t>When the sunlight strikes raindrops in the air, they act as a prism and form a rainbow. The rainbow is a division of white light into many beautiful colors. These take the shape of a long round arch, with its path high above, and its two ends apparently beyond the horizon. There is, according to legend, a boiling pot of gold at one end. People look, but no one ever finds it. When a man looks for something beyond his reach, his friends say he is looking for the pot of gold at the end of the rainbow.</t>
   </si>
   <si>
-    <t>LESEN_SAETZE.wav</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Hier ist der zweite Satz:
-„Die Schar Kinder nimmt die Schere mit in die Schule.“
-Bitte lesen Sie die folgenden Sätze.</t>
-  </si>
-  <si>
-    <t>Die Schar Kinder nimmt die Schere mit in die Schule.</t>
-  </si>
-  <si>
-    <t>LESEN_SAETZE_SH.wav</t>
-  </si>
-  <si>
-    <t>RFF_SH</t>
-  </si>
-  <si>
-    <t>Bitte sagen Sie jetzt fünf Sekunden lang durchgängig  "Ah".</t>
-  </si>
-  <si>
-    <t>AH [5 Sekunden]</t>
-  </si>
-  <si>
-    <t>AH.wav</t>
-  </si>
-  <si>
-    <t>AH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     </t>
-  </si>
-  <si>
-    <t>SpeechIntroText</t>
+    <t xml:space="preserve">Using your natural voice with comfortable pitch and loudness, read the following text. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica"/>
     </font>
   </fonts>
   <fills count="3">
@@ -143,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -166,135 +112,15 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="9"/>
-      </left>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="9"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="9"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="9"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="9"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1455,7 +1281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.375" style="1" customWidth="1"/>
@@ -1467,7 +1293,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1479,275 +1305,41 @@
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0</v>
       </c>
       <c r="F2" s="3">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H2" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="3">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="3">
-        <v>1</v>
-      </c>
-      <c r="F4" s="3">
-        <v>2</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3">
-        <v>3</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="11.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="3">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3">
-        <v>2</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1</v>
-      </c>
-      <c r="F8" s="3">
-        <v>3</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="10">
-        <v>2</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="11">
-        <v>2</v>
-      </c>
-      <c r="F10" s="12">
-        <v>2</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="11">
-        <v>2</v>
-      </c>
-      <c r="F11" s="14">
-        <v>3</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11" s="3">
         <v>1</v>
       </c>
     </row>
